--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post DFS_HRM-2031-0120/Panel-28/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post DFS_HRM-2031-0120/Panel-28/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.81109</v>
+        <v>16.93061</v>
       </c>
       <c r="D2" t="n">
-        <v>16.69834</v>
+        <v>16.37321</v>
       </c>
       <c r="E2" t="n">
-        <v>16.73468</v>
+        <v>16.81456</v>
       </c>
       <c r="F2" t="n">
-        <v>41.75521</v>
+        <v>42.54947</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05048</v>
+        <v>0.05078</v>
       </c>
       <c r="H2" t="n">
-        <v>1.82762</v>
+        <v>1.80354</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.70216</v>
+        <v>16.81947</v>
       </c>
       <c r="D3" t="n">
-        <v>16.76042</v>
+        <v>16.53187</v>
       </c>
       <c r="E3" t="n">
-        <v>16.79642</v>
+        <v>16.68892</v>
       </c>
       <c r="F3" t="n">
-        <v>42.90606</v>
+        <v>42.24291</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05125</v>
+        <v>0.05123</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81926</v>
+        <v>1.81778</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.53969</v>
+        <v>16.86676</v>
       </c>
       <c r="D4" t="n">
-        <v>16.54117</v>
+        <v>16.25567</v>
       </c>
       <c r="E4" t="n">
-        <v>16.43855</v>
+        <v>16.78182</v>
       </c>
       <c r="F4" t="n">
-        <v>43.07155</v>
+        <v>42.51334</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05055</v>
+        <v>0.05098</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83545</v>
+        <v>1.82646</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.65167</v>
+        <v>17.00175</v>
       </c>
       <c r="D6" t="n">
-        <v>15.83847</v>
+        <v>15.78525</v>
       </c>
       <c r="E6" t="n">
-        <v>16.10995</v>
+        <v>16.51611</v>
       </c>
       <c r="F6" t="n">
-        <v>21.99544</v>
+        <v>21.6898</v>
       </c>
       <c r="G6" t="n">
-        <v>33.67473</v>
+        <v>34.30285</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.87189</v>
+        <v>16.70418</v>
       </c>
       <c r="D7" t="n">
-        <v>15.87691</v>
+        <v>15.90646</v>
       </c>
       <c r="E7" t="n">
-        <v>16.51191</v>
+        <v>16.48891</v>
       </c>
       <c r="F7" t="n">
-        <v>21.81853</v>
+        <v>21.45246</v>
       </c>
       <c r="G7" t="n">
-        <v>33.6779</v>
+        <v>34.21569</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.89351</v>
+        <v>16.79591</v>
       </c>
       <c r="D8" t="n">
-        <v>16.18576</v>
+        <v>16.06206</v>
       </c>
       <c r="E8" t="n">
-        <v>16.26578</v>
+        <v>16.16393</v>
       </c>
       <c r="F8" t="n">
-        <v>21.83287</v>
+        <v>21.64771</v>
       </c>
       <c r="G8" t="n">
-        <v>33.52041</v>
+        <v>34.73143</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.61721</v>
+        <v>0.6133</v>
       </c>
       <c r="D10" t="n">
-        <v>1.10369</v>
+        <v>1.12024</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.60732</v>
+        <v>0.60609</v>
       </c>
       <c r="D11" t="n">
-        <v>1.11125</v>
+        <v>1.12701</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.59877</v>
+        <v>0.60371</v>
       </c>
       <c r="D12" t="n">
-        <v>1.09331</v>
+        <v>1.12565</v>
       </c>
     </row>
   </sheetData>
